--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/test/resources/asset/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{02A84BF3-4F83-B14D-A945-4192CDFC3E09}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{45001F91-B78F-4977-A5B7-B96DBA78E0CD}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -516,10 +516,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
-    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
-    <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
+    <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -1128,7 +1128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
@@ -1152,7 +1152,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1188,7 +1188,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1">
@@ -1215,7 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
@@ -2075,63 +2075,63 @@
     <tabColor theme="4"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BI4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:BP4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="8" width="13.5" style="71" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="8" width="13.44140625" style="71" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="71" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.33203125" style="71" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" style="74" customWidth="1"/>
-    <col min="14" max="14" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" style="74" customWidth="1"/>
+    <col min="14" max="14" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
     <col min="17" max="17" width="19" style="71" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="10" style="71" customWidth="1"/>
-    <col min="20" max="21" width="10.1640625" customWidth="1"/>
-    <col min="22" max="22" width="19.1640625" customWidth="1"/>
-    <col min="23" max="23" width="19.1640625" style="71" customWidth="1"/>
+    <col min="20" max="21" width="10.109375" customWidth="1"/>
+    <col min="22" max="22" width="19.109375" customWidth="1"/>
+    <col min="23" max="23" width="19.109375" style="71" customWidth="1"/>
     <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="10.1640625" customWidth="1"/>
+    <col min="25" max="26" width="10.109375" customWidth="1"/>
     <col min="27" max="27" width="13.6640625" customWidth="1"/>
-    <col min="28" max="28" width="17.5" customWidth="1"/>
-    <col min="29" max="29" width="14.5" customWidth="1"/>
-    <col min="30" max="30" width="11.1640625" customWidth="1"/>
+    <col min="28" max="28" width="17.44140625" customWidth="1"/>
+    <col min="29" max="29" width="14.44140625" customWidth="1"/>
+    <col min="30" max="30" width="11.109375" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
-    <col min="33" max="33" width="10.1640625" customWidth="1"/>
-    <col min="34" max="34" width="11.5" customWidth="1"/>
-    <col min="35" max="35" width="11.5" style="71" customWidth="1"/>
-    <col min="36" max="36" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" customWidth="1"/>
+    <col min="33" max="33" width="10.109375" customWidth="1"/>
+    <col min="34" max="34" width="11.44140625" customWidth="1"/>
+    <col min="35" max="35" width="11.44140625" style="71" customWidth="1"/>
+    <col min="36" max="36" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.33203125" customWidth="1"/>
     <col min="38" max="38" width="14.6640625" customWidth="1"/>
-    <col min="39" max="39" width="12.5" customWidth="1"/>
+    <col min="39" max="39" width="12.44140625" customWidth="1"/>
     <col min="40" max="40" width="12.6640625" customWidth="1"/>
     <col min="41" max="42" width="12.33203125" style="74" customWidth="1"/>
-    <col min="43" max="43" width="16.1640625" style="74" customWidth="1"/>
-    <col min="44" max="44" width="12.83203125" style="74" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.1640625" style="74" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.109375" style="74" customWidth="1"/>
+    <col min="44" max="44" width="12.77734375" style="74" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.109375" style="74" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="11.6640625" customWidth="1"/>
-    <col min="53" max="54" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="11.33203125" customWidth="1"/>
     <col min="56" max="57" width="11.33203125" style="71" customWidth="1"/>
-    <col min="58" max="58" width="27.5" customWidth="1"/>
-    <col min="59" max="59" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="27.44140625" customWidth="1"/>
+    <col min="59" max="59" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="27" hidden="1" customHeight="1">
+    <row r="1" spans="1:68" ht="27" hidden="1" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>34</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="M1" s="76"/>
       <c r="BG1" s="76"/>
     </row>
-    <row r="2" spans="1:61" ht="14">
+    <row r="2" spans="1:68" ht="15.75">
       <c r="A2" s="77"/>
       <c r="B2" s="79" t="s">
         <v>101</v>
@@ -2175,7 +2175,7 @@
       <c r="M2" s="76"/>
       <c r="BG2" s="76"/>
     </row>
-    <row r="3" spans="1:61" ht="34" thickBot="1">
+    <row r="3" spans="1:68" ht="33.75" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2239,8 +2239,15 @@
       <c r="BG3" s="1"/>
       <c r="BH3" s="72"/>
       <c r="BI3" s="72"/>
-    </row>
-    <row r="4" spans="1:61" ht="14">
+      <c r="BJ3" s="72"/>
+      <c r="BK3" s="72"/>
+      <c r="BL3" s="72"/>
+      <c r="BM3" s="72"/>
+      <c r="BN3" s="72"/>
+      <c r="BO3" s="72"/>
+      <c r="BP3" s="72"/>
+    </row>
+    <row r="4" spans="1:68" ht="15.75">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2291,12 +2298,12 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" thickBot="1">
+    <row r="1" spans="1:1" ht="33.75" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -2334,14 +2341,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" thickBot="1">
+    <row r="1" spans="1:5" ht="33.75" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2640,16 +2647,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="35" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="35"/>
-    <col min="4" max="4" width="27.83203125" style="35" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="35"/>
+    <col min="3" max="3" width="8.77734375" style="35"/>
+    <col min="4" max="4" width="27.77734375" style="35" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1">
       <c r="A1" s="81" t="s">
         <v>68</v>
       </c>
@@ -2657,7 +2664,7 @@
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
     </row>
-    <row r="2" spans="1:4" ht="18" thickBot="1">
+    <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="36" t="s">
         <v>69</v>
       </c>
@@ -2671,7 +2678,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="17">
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -2683,7 +2690,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1">
+    <row r="4" spans="1:4" ht="17.25" thickBot="1">
       <c r="A4" s="42">
         <v>2</v>
       </c>
@@ -2695,7 +2702,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" thickBot="1">
+    <row r="5" spans="1:4" ht="17.25" thickBot="1">
       <c r="A5" s="42">
         <v>3</v>
       </c>
@@ -2707,13 +2714,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+    <row r="6" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
       <c r="A6" s="46"/>
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
     </row>
-    <row r="7" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+    <row r="7" spans="1:4" s="49" customFormat="1" ht="16.5" thickBot="1">
       <c r="A7" s="82" t="s">
         <v>76</v>
       </c>
@@ -2721,7 +2728,7 @@
       <c r="C7" s="83"/>
       <c r="D7" s="84"/>
     </row>
-    <row r="8" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+    <row r="8" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
       <c r="A8" s="50" t="s">
         <v>69</v>
       </c>
@@ -2735,7 +2742,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="17">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="52">
         <v>3</v>
       </c>
@@ -2745,7 +2752,7 @@
       <c r="C9" s="54"/>
       <c r="D9" s="55"/>
     </row>
-    <row r="10" spans="1:4" ht="17">
+    <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="38">
         <v>4</v>
       </c>
@@ -2755,7 +2762,7 @@
       <c r="C10" s="56"/>
       <c r="D10" s="57"/>
     </row>
-    <row r="11" spans="1:4" ht="18" thickBot="1">
+    <row r="11" spans="1:4" ht="17.25" thickBot="1">
       <c r="A11" s="38">
         <v>5</v>
       </c>
@@ -2765,7 +2772,7 @@
       <c r="C11" s="56"/>
       <c r="D11" s="57"/>
     </row>
-    <row r="12" spans="1:4" ht="17">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="52">
         <v>6</v>
       </c>
@@ -2775,7 +2782,7 @@
       <c r="C12" s="56"/>
       <c r="D12" s="57"/>
     </row>
-    <row r="13" spans="1:4" ht="17">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="38">
         <v>7</v>
       </c>
@@ -2785,7 +2792,7 @@
       <c r="C13" s="56"/>
       <c r="D13" s="57"/>
     </row>
-    <row r="14" spans="1:4" ht="18" thickBot="1">
+    <row r="14" spans="1:4" ht="17.25" thickBot="1">
       <c r="A14" s="38">
         <v>8</v>
       </c>
@@ -2795,7 +2802,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="57"/>
     </row>
-    <row r="15" spans="1:4" ht="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="52">
         <v>9</v>
       </c>
@@ -2805,7 +2812,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="57"/>
     </row>
-    <row r="16" spans="1:4" ht="17">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="38">
         <v>10</v>
       </c>
@@ -2815,7 +2822,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="57"/>
     </row>
-    <row r="17" spans="1:4" ht="18" thickBot="1">
+    <row r="17" spans="1:4" ht="17.25" thickBot="1">
       <c r="A17" s="38">
         <v>11</v>
       </c>
@@ -2827,7 +2834,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="52">
         <v>12</v>
       </c>
@@ -2837,7 +2844,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="57"/>
     </row>
-    <row r="19" spans="1:4" ht="17">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="38">
         <v>13</v>
       </c>
@@ -2847,7 +2854,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="57"/>
     </row>
-    <row r="20" spans="1:4" ht="18" thickBot="1">
+    <row r="20" spans="1:4" ht="17.25" thickBot="1">
       <c r="A20" s="38">
         <v>14</v>
       </c>
@@ -2857,7 +2864,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="57"/>
     </row>
-    <row r="21" spans="1:4" ht="17">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="52">
         <v>15</v>
       </c>
@@ -2867,7 +2874,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="57"/>
     </row>
-    <row r="22" spans="1:4" ht="18" thickBot="1">
+    <row r="22" spans="1:4" ht="17.25" thickBot="1">
       <c r="A22" s="38">
         <v>16</v>
       </c>
@@ -2877,10 +2884,10 @@
       <c r="C22" s="58"/>
       <c r="D22" s="59"/>
     </row>
-    <row r="23" spans="1:4" ht="16" thickBot="1">
+    <row r="23" spans="1:4" ht="16.5" thickBot="1">
       <c r="A23" s="60"/>
     </row>
-    <row r="24" spans="1:4" ht="18" thickBot="1">
+    <row r="24" spans="1:4" ht="16.5" thickBot="1">
       <c r="A24" s="85" t="s">
         <v>92</v>
       </c>
@@ -2888,7 +2895,7 @@
       <c r="C24" s="86"/>
       <c r="D24" s="87"/>
     </row>
-    <row r="25" spans="1:4" ht="18" thickBot="1">
+    <row r="25" spans="1:4" ht="17.25" thickBot="1">
       <c r="A25" s="61" t="s">
         <v>69</v>
       </c>
@@ -2902,7 +2909,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16" thickBot="1">
+    <row r="26" spans="1:4" ht="16.5" thickBot="1">
       <c r="A26" s="38">
         <v>17</v>
       </c>
@@ -2914,7 +2921,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16" thickBot="1">
+    <row r="27" spans="1:4" ht="16.5" thickBot="1">
       <c r="A27" s="38">
         <v>18</v>
       </c>
@@ -2926,7 +2933,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15">
+    <row r="28" spans="1:4">
       <c r="A28" s="38">
         <v>19</v>
       </c>
@@ -2938,7 +2945,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16" thickBot="1">
+    <row r="29" spans="1:4" ht="16.5" thickBot="1">
       <c r="A29" s="38">
         <v>20</v>
       </c>
@@ -2972,11 +2979,11 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="30" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="30" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3002,7 +3009,7 @@
       </c>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="1:4" ht="16">
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="17" t="s">
         <v>35</v>
       </c>
@@ -3014,7 +3021,7 @@
       </c>
       <c r="D3" s="19"/>
     </row>
-    <row r="4" spans="1:4" ht="16">
+    <row r="4" spans="1:4" ht="16.5">
       <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
@@ -3026,7 +3033,7 @@
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="16">
+    <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="21" t="s">
         <v>13</v>
       </c>
@@ -3034,7 +3041,7 @@
       <c r="C5" s="22"/>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="16">
+    <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="23" t="s">
         <v>49</v>
       </c>
@@ -3046,7 +3053,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16">
+    <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="21" t="s">
         <v>52</v>
       </c>
@@ -3054,7 +3061,7 @@
       <c r="C7" s="24"/>
       <c r="D7" s="19"/>
     </row>
-    <row r="8" spans="1:4" ht="16">
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="23" t="s">
         <v>53</v>
       </c>
@@ -3064,7 +3071,7 @@
       </c>
       <c r="D8" s="19"/>
     </row>
-    <row r="9" spans="1:4" ht="16">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="26" t="s">
         <v>26</v>
       </c>
@@ -3076,7 +3083,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16">
+    <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="23" t="s">
         <v>56</v>
       </c>
@@ -3086,7 +3093,7 @@
       </c>
       <c r="D10" s="19"/>
     </row>
-    <row r="11" spans="1:4" ht="16">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="21" t="s">
         <v>15</v>
       </c>
@@ -3094,7 +3101,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="19"/>
     </row>
-    <row r="12" spans="1:4" ht="16">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="23" t="s">
         <v>27</v>
       </c>
@@ -3104,7 +3111,7 @@
       </c>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" ht="16">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="17" t="s">
         <v>28</v>
       </c>
@@ -3116,7 +3123,7 @@
       </c>
       <c r="D13" s="19"/>
     </row>
-    <row r="14" spans="1:4" ht="16">
+    <row r="14" spans="1:4" ht="16.5">
       <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
@@ -3124,7 +3131,7 @@
       <c r="C14" s="25"/>
       <c r="D14" s="19"/>
     </row>
-    <row r="15" spans="1:4" ht="16">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="23" t="s">
         <v>58</v>
       </c>
@@ -3134,7 +3141,7 @@
       </c>
       <c r="D15" s="19"/>
     </row>
-    <row r="16" spans="1:4" ht="16">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="21" t="s">
         <v>30</v>
       </c>
@@ -3142,7 +3149,7 @@
       <c r="C16" s="25"/>
       <c r="D16" s="19"/>
     </row>
-    <row r="17" spans="1:4" ht="16">
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="23" t="s">
         <v>59</v>
       </c>
@@ -3152,7 +3159,7 @@
       </c>
       <c r="D17" s="19"/>
     </row>
-    <row r="18" spans="1:4" ht="16">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="23" t="s">
         <v>31</v>
       </c>
@@ -3162,7 +3169,7 @@
       </c>
       <c r="D18" s="19"/>
     </row>
-    <row r="19" spans="1:4" ht="16">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="21" t="s">
         <v>32</v>
       </c>
@@ -3170,7 +3177,7 @@
       <c r="C19" s="25"/>
       <c r="D19" s="19"/>
     </row>
-    <row r="20" spans="1:4" ht="16">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="23" t="s">
         <v>33</v>
       </c>
@@ -3180,7 +3187,7 @@
       </c>
       <c r="D20" s="19"/>
     </row>
-    <row r="21" spans="1:4" ht="16">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="26" t="s">
         <v>10</v>
       </c>
@@ -3190,7 +3197,7 @@
       </c>
       <c r="D21" s="19"/>
     </row>
-    <row r="22" spans="1:4" ht="16">
+    <row r="22" spans="1:4" ht="16.5">
       <c r="A22" s="21" t="s">
         <v>16</v>
       </c>
@@ -3198,7 +3205,7 @@
       <c r="C22" s="25"/>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" spans="1:4" ht="16">
+    <row r="23" spans="1:4" ht="16.5">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3206,7 +3213,7 @@
       <c r="C23" s="25"/>
       <c r="D23" s="19"/>
     </row>
-    <row r="24" spans="1:4" ht="16">
+    <row r="24" spans="1:4" ht="16.5">
       <c r="A24" s="21" t="s">
         <v>18</v>
       </c>
@@ -3214,7 +3221,7 @@
       <c r="C24" s="25"/>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:4" ht="16">
+    <row r="25" spans="1:4" ht="16.5">
       <c r="A25" s="21" t="s">
         <v>19</v>
       </c>
@@ -3222,7 +3229,7 @@
       <c r="C25" s="25"/>
       <c r="D25" s="19"/>
     </row>
-    <row r="26" spans="1:4" ht="16">
+    <row r="26" spans="1:4" ht="16.5">
       <c r="A26" s="21" t="s">
         <v>20</v>
       </c>
@@ -3230,7 +3237,7 @@
       <c r="C26" s="25"/>
       <c r="D26" s="19"/>
     </row>
-    <row r="27" spans="1:4" ht="16">
+    <row r="27" spans="1:4" ht="16.5">
       <c r="A27" s="21" t="s">
         <v>21</v>
       </c>
@@ -3238,7 +3245,7 @@
       <c r="C27" s="25"/>
       <c r="D27" s="19"/>
     </row>
-    <row r="28" spans="1:4" ht="16">
+    <row r="28" spans="1:4" ht="16.5">
       <c r="A28" s="23" t="s">
         <v>22</v>
       </c>
@@ -3248,7 +3255,7 @@
       </c>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="1:4" ht="16">
+    <row r="29" spans="1:4" ht="16.5">
       <c r="A29" s="23" t="s">
         <v>23</v>
       </c>
@@ -3258,7 +3265,7 @@
       </c>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:4" ht="16">
+    <row r="30" spans="1:4" ht="16.5">
       <c r="A30" s="21" t="s">
         <v>24</v>
       </c>
@@ -3266,7 +3273,7 @@
       <c r="C30" s="25"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:4" ht="16">
+    <row r="31" spans="1:4" ht="16.5">
       <c r="A31" s="21" t="s">
         <v>102</v>
       </c>
@@ -3274,7 +3281,7 @@
       <c r="C31" s="25"/>
       <c r="D31" s="19"/>
     </row>
-    <row r="32" spans="1:4" ht="16">
+    <row r="32" spans="1:4" ht="16.5">
       <c r="A32" s="21" t="s">
         <v>25</v>
       </c>
@@ -3282,7 +3289,7 @@
       <c r="C32" s="25"/>
       <c r="D32" s="19"/>
     </row>
-    <row r="33" spans="1:4" ht="16">
+    <row r="33" spans="1:4" ht="16.5">
       <c r="A33" s="21" t="s">
         <v>105</v>
       </c>
@@ -3290,7 +3297,7 @@
       <c r="C33" s="25"/>
       <c r="D33" s="19"/>
     </row>
-    <row r="34" spans="1:4" ht="16">
+    <row r="34" spans="1:4" ht="16.5">
       <c r="A34" s="21" t="s">
         <v>103</v>
       </c>
@@ -3298,7 +3305,7 @@
       <c r="C34" s="25"/>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="1:4" ht="16">
+    <row r="35" spans="1:4" ht="16.5">
       <c r="A35" s="21" t="s">
         <v>104</v>
       </c>
@@ -3306,7 +3313,7 @@
       <c r="C35" s="25"/>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="1:4" ht="16">
+    <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="28" t="s">
         <v>61</v>
       </c>
@@ -3321,7 +3328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15">
+    <row r="40" spans="1:4">
       <c r="A40" s="31"/>
       <c r="B40" t="s">
         <v>63</v>
@@ -3330,7 +3337,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15">
+    <row r="41" spans="1:4">
       <c r="A41" s="33"/>
       <c r="B41" t="s">
         <v>65</v>
@@ -3339,7 +3346,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15">
+    <row r="42" spans="1:4">
       <c r="A42" s="34"/>
       <c r="B42" t="s">
         <v>66</v>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10610"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\resources\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/resources/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{45001F91-B78F-4977-A5B7-B96DBA78E0CD}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{094F6CBD-183C-3D4E-93BE-7745BBB488DB}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -516,10 +516,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
+    <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -1128,7 +1128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
@@ -1152,7 +1152,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1188,7 +1188,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1">
@@ -1215,7 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
@@ -2075,63 +2075,63 @@
     <tabColor theme="4"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BP4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:BQ4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="8" width="13.44140625" style="71" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="8" width="13.5" style="71" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="71" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.33203125" style="71" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" customWidth="1"/>
-    <col min="13" max="13" width="18.77734375" style="74" customWidth="1"/>
-    <col min="14" max="14" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" style="74" customWidth="1"/>
+    <col min="14" max="14" width="22.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
     <col min="17" max="17" width="19" style="71" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="10" style="71" customWidth="1"/>
-    <col min="20" max="21" width="10.109375" customWidth="1"/>
-    <col min="22" max="22" width="19.109375" customWidth="1"/>
-    <col min="23" max="23" width="19.109375" style="71" customWidth="1"/>
+    <col min="20" max="21" width="10.1640625" customWidth="1"/>
+    <col min="22" max="22" width="19.1640625" customWidth="1"/>
+    <col min="23" max="23" width="19.1640625" style="71" customWidth="1"/>
     <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="10.109375" customWidth="1"/>
+    <col min="25" max="26" width="10.1640625" customWidth="1"/>
     <col min="27" max="27" width="13.6640625" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" customWidth="1"/>
-    <col min="29" max="29" width="14.44140625" customWidth="1"/>
-    <col min="30" max="30" width="11.109375" customWidth="1"/>
+    <col min="28" max="28" width="17.5" customWidth="1"/>
+    <col min="29" max="29" width="14.5" customWidth="1"/>
+    <col min="30" max="30" width="11.1640625" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" customWidth="1"/>
-    <col min="33" max="33" width="10.109375" customWidth="1"/>
-    <col min="34" max="34" width="11.44140625" customWidth="1"/>
-    <col min="35" max="35" width="11.44140625" style="71" customWidth="1"/>
-    <col min="36" max="36" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.5" customWidth="1"/>
+    <col min="33" max="33" width="10.1640625" customWidth="1"/>
+    <col min="34" max="34" width="11.5" customWidth="1"/>
+    <col min="35" max="35" width="11.5" style="71" customWidth="1"/>
+    <col min="36" max="36" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.33203125" customWidth="1"/>
     <col min="38" max="38" width="14.6640625" customWidth="1"/>
-    <col min="39" max="39" width="12.44140625" customWidth="1"/>
+    <col min="39" max="39" width="12.5" customWidth="1"/>
     <col min="40" max="40" width="12.6640625" customWidth="1"/>
     <col min="41" max="42" width="12.33203125" style="74" customWidth="1"/>
-    <col min="43" max="43" width="16.109375" style="74" customWidth="1"/>
-    <col min="44" max="44" width="12.77734375" style="74" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.1640625" style="74" customWidth="1"/>
+    <col min="44" max="44" width="12.83203125" style="74" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.1640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="11.6640625" customWidth="1"/>
-    <col min="53" max="54" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="11.33203125" customWidth="1"/>
     <col min="56" max="57" width="11.33203125" style="71" customWidth="1"/>
-    <col min="58" max="58" width="27.44140625" customWidth="1"/>
-    <col min="59" max="59" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="27.5" customWidth="1"/>
+    <col min="59" max="59" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="27" hidden="1" customHeight="1">
+    <row r="1" spans="1:69" ht="27" hidden="1" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>34</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="M1" s="76"/>
       <c r="BG1" s="76"/>
     </row>
-    <row r="2" spans="1:68" ht="15.75">
+    <row r="2" spans="1:69" ht="14">
       <c r="A2" s="77"/>
       <c r="B2" s="79" t="s">
         <v>101</v>
@@ -2175,7 +2175,7 @@
       <c r="M2" s="76"/>
       <c r="BG2" s="76"/>
     </row>
-    <row r="3" spans="1:68" ht="33.75" thickBot="1">
+    <row r="3" spans="1:69" ht="34" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2246,8 +2246,9 @@
       <c r="BN3" s="72"/>
       <c r="BO3" s="72"/>
       <c r="BP3" s="72"/>
-    </row>
-    <row r="4" spans="1:68" ht="15.75">
+      <c r="BQ3" s="72"/>
+    </row>
+    <row r="4" spans="1:69" ht="14">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2298,12 +2299,12 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.75" thickBot="1">
+    <row r="1" spans="1:1" ht="34" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -2341,14 +2342,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.75" thickBot="1">
+    <row r="1" spans="1:5" ht="34" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2647,16 +2648,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="35" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="35" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="35"/>
-    <col min="4" max="4" width="27.77734375" style="35" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="35"/>
+    <col min="3" max="3" width="8.83203125" style="35"/>
+    <col min="4" max="4" width="27.83203125" style="35" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" thickBot="1">
+    <row r="1" spans="1:4" ht="18" thickBot="1">
       <c r="A1" s="81" t="s">
         <v>68</v>
       </c>
@@ -2664,7 +2665,7 @@
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
     </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1">
+    <row r="2" spans="1:4" ht="18" thickBot="1">
       <c r="A2" s="36" t="s">
         <v>69</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3" s="38">
         <v>1</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1">
+    <row r="4" spans="1:4" ht="18" thickBot="1">
       <c r="A4" s="42">
         <v>2</v>
       </c>
@@ -2702,7 +2703,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1">
+    <row r="5" spans="1:4" ht="18" thickBot="1">
       <c r="A5" s="42">
         <v>3</v>
       </c>
@@ -2714,13 +2715,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
+    <row r="6" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
       <c r="A6" s="46"/>
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
     </row>
-    <row r="7" spans="1:4" s="49" customFormat="1" ht="16.5" thickBot="1">
+    <row r="7" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
       <c r="A7" s="82" t="s">
         <v>76</v>
       </c>
@@ -2728,7 +2729,7 @@
       <c r="C7" s="83"/>
       <c r="D7" s="84"/>
     </row>
-    <row r="8" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
+    <row r="8" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
       <c r="A8" s="50" t="s">
         <v>69</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="17">
       <c r="A9" s="52">
         <v>3</v>
       </c>
@@ -2752,7 +2753,7 @@
       <c r="C9" s="54"/>
       <c r="D9" s="55"/>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
+    <row r="10" spans="1:4" ht="17">
       <c r="A10" s="38">
         <v>4</v>
       </c>
@@ -2762,7 +2763,7 @@
       <c r="C10" s="56"/>
       <c r="D10" s="57"/>
     </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1">
+    <row r="11" spans="1:4" ht="18" thickBot="1">
       <c r="A11" s="38">
         <v>5</v>
       </c>
@@ -2772,7 +2773,7 @@
       <c r="C11" s="56"/>
       <c r="D11" s="57"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5">
+    <row r="12" spans="1:4" ht="17">
       <c r="A12" s="52">
         <v>6</v>
       </c>
@@ -2782,7 +2783,7 @@
       <c r="C12" s="56"/>
       <c r="D12" s="57"/>
     </row>
-    <row r="13" spans="1:4" ht="16.5">
+    <row r="13" spans="1:4" ht="17">
       <c r="A13" s="38">
         <v>7</v>
       </c>
@@ -2792,7 +2793,7 @@
       <c r="C13" s="56"/>
       <c r="D13" s="57"/>
     </row>
-    <row r="14" spans="1:4" ht="17.25" thickBot="1">
+    <row r="14" spans="1:4" ht="18" thickBot="1">
       <c r="A14" s="38">
         <v>8</v>
       </c>
@@ -2802,7 +2803,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="57"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="15">
       <c r="A15" s="52">
         <v>9</v>
       </c>
@@ -2812,7 +2813,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="57"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5">
+    <row r="16" spans="1:4" ht="17">
       <c r="A16" s="38">
         <v>10</v>
       </c>
@@ -2822,7 +2823,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="57"/>
     </row>
-    <row r="17" spans="1:4" ht="17.25" thickBot="1">
+    <row r="17" spans="1:4" ht="18" thickBot="1">
       <c r="A17" s="38">
         <v>11</v>
       </c>
@@ -2834,7 +2835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5">
+    <row r="18" spans="1:4" ht="17">
       <c r="A18" s="52">
         <v>12</v>
       </c>
@@ -2844,7 +2845,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="57"/>
     </row>
-    <row r="19" spans="1:4" ht="16.5">
+    <row r="19" spans="1:4" ht="17">
       <c r="A19" s="38">
         <v>13</v>
       </c>
@@ -2854,7 +2855,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="57"/>
     </row>
-    <row r="20" spans="1:4" ht="17.25" thickBot="1">
+    <row r="20" spans="1:4" ht="18" thickBot="1">
       <c r="A20" s="38">
         <v>14</v>
       </c>
@@ -2864,7 +2865,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="57"/>
     </row>
-    <row r="21" spans="1:4" ht="16.5">
+    <row r="21" spans="1:4" ht="17">
       <c r="A21" s="52">
         <v>15</v>
       </c>
@@ -2874,7 +2875,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="57"/>
     </row>
-    <row r="22" spans="1:4" ht="17.25" thickBot="1">
+    <row r="22" spans="1:4" ht="18" thickBot="1">
       <c r="A22" s="38">
         <v>16</v>
       </c>
@@ -2884,10 +2885,10 @@
       <c r="C22" s="58"/>
       <c r="D22" s="59"/>
     </row>
-    <row r="23" spans="1:4" ht="16.5" thickBot="1">
+    <row r="23" spans="1:4" ht="16" thickBot="1">
       <c r="A23" s="60"/>
     </row>
-    <row r="24" spans="1:4" ht="16.5" thickBot="1">
+    <row r="24" spans="1:4" ht="18" thickBot="1">
       <c r="A24" s="85" t="s">
         <v>92</v>
       </c>
@@ -2895,7 +2896,7 @@
       <c r="C24" s="86"/>
       <c r="D24" s="87"/>
     </row>
-    <row r="25" spans="1:4" ht="17.25" thickBot="1">
+    <row r="25" spans="1:4" ht="18" thickBot="1">
       <c r="A25" s="61" t="s">
         <v>69</v>
       </c>
@@ -2909,7 +2910,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16.5" thickBot="1">
+    <row r="26" spans="1:4" ht="16" thickBot="1">
       <c r="A26" s="38">
         <v>17</v>
       </c>
@@ -2921,7 +2922,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" thickBot="1">
+    <row r="27" spans="1:4" ht="16" thickBot="1">
       <c r="A27" s="38">
         <v>18</v>
       </c>
@@ -2933,7 +2934,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" ht="15">
       <c r="A28" s="38">
         <v>19</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" thickBot="1">
+    <row r="29" spans="1:4" ht="16" thickBot="1">
       <c r="A29" s="38">
         <v>20</v>
       </c>
@@ -2979,11 +2980,11 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="30" customWidth="1"/>
+    <col min="1" max="1" width="19.5" style="30" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3009,7 +3010,7 @@
       </c>
       <c r="D2" s="88"/>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4" ht="16">
       <c r="A3" s="17" t="s">
         <v>35</v>
       </c>
@@ -3021,7 +3022,7 @@
       </c>
       <c r="D3" s="19"/>
     </row>
-    <row r="4" spans="1:4" ht="16.5">
+    <row r="4" spans="1:4" ht="16">
       <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
@@ -3033,7 +3034,7 @@
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="16.5">
+    <row r="5" spans="1:4" ht="16">
       <c r="A5" s="21" t="s">
         <v>13</v>
       </c>
@@ -3041,7 +3042,7 @@
       <c r="C5" s="22"/>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="16.5">
+    <row r="6" spans="1:4" ht="16">
       <c r="A6" s="23" t="s">
         <v>49</v>
       </c>
@@ -3053,7 +3054,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5">
+    <row r="7" spans="1:4" ht="16">
       <c r="A7" s="21" t="s">
         <v>52</v>
       </c>
@@ -3061,7 +3062,7 @@
       <c r="C7" s="24"/>
       <c r="D7" s="19"/>
     </row>
-    <row r="8" spans="1:4" ht="16.5">
+    <row r="8" spans="1:4" ht="16">
       <c r="A8" s="23" t="s">
         <v>53</v>
       </c>
@@ -3071,7 +3072,7 @@
       </c>
       <c r="D8" s="19"/>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="16">
       <c r="A9" s="26" t="s">
         <v>26</v>
       </c>
@@ -3083,7 +3084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
+    <row r="10" spans="1:4" ht="16">
       <c r="A10" s="23" t="s">
         <v>56</v>
       </c>
@@ -3093,7 +3094,7 @@
       </c>
       <c r="D10" s="19"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
+    <row r="11" spans="1:4" ht="16">
       <c r="A11" s="21" t="s">
         <v>15</v>
       </c>
@@ -3101,7 +3102,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="19"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5">
+    <row r="12" spans="1:4" ht="16">
       <c r="A12" s="23" t="s">
         <v>27</v>
       </c>
@@ -3111,7 +3112,7 @@
       </c>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" ht="16.5">
+    <row r="13" spans="1:4" ht="16">
       <c r="A13" s="17" t="s">
         <v>28</v>
       </c>
@@ -3123,7 +3124,7 @@
       </c>
       <c r="D13" s="19"/>
     </row>
-    <row r="14" spans="1:4" ht="16.5">
+    <row r="14" spans="1:4" ht="16">
       <c r="A14" s="21" t="s">
         <v>29</v>
       </c>
@@ -3131,7 +3132,7 @@
       <c r="C14" s="25"/>
       <c r="D14" s="19"/>
     </row>
-    <row r="15" spans="1:4" ht="16.5">
+    <row r="15" spans="1:4" ht="16">
       <c r="A15" s="23" t="s">
         <v>58</v>
       </c>
@@ -3141,7 +3142,7 @@
       </c>
       <c r="D15" s="19"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5">
+    <row r="16" spans="1:4" ht="16">
       <c r="A16" s="21" t="s">
         <v>30</v>
       </c>
@@ -3149,7 +3150,7 @@
       <c r="C16" s="25"/>
       <c r="D16" s="19"/>
     </row>
-    <row r="17" spans="1:4" ht="16.5">
+    <row r="17" spans="1:4" ht="16">
       <c r="A17" s="23" t="s">
         <v>59</v>
       </c>
@@ -3159,7 +3160,7 @@
       </c>
       <c r="D17" s="19"/>
     </row>
-    <row r="18" spans="1:4" ht="16.5">
+    <row r="18" spans="1:4" ht="16">
       <c r="A18" s="23" t="s">
         <v>31</v>
       </c>
@@ -3169,7 +3170,7 @@
       </c>
       <c r="D18" s="19"/>
     </row>
-    <row r="19" spans="1:4" ht="16.5">
+    <row r="19" spans="1:4" ht="16">
       <c r="A19" s="21" t="s">
         <v>32</v>
       </c>
@@ -3177,7 +3178,7 @@
       <c r="C19" s="25"/>
       <c r="D19" s="19"/>
     </row>
-    <row r="20" spans="1:4" ht="16.5">
+    <row r="20" spans="1:4" ht="16">
       <c r="A20" s="23" t="s">
         <v>33</v>
       </c>
@@ -3187,7 +3188,7 @@
       </c>
       <c r="D20" s="19"/>
     </row>
-    <row r="21" spans="1:4" ht="16.5">
+    <row r="21" spans="1:4" ht="16">
       <c r="A21" s="26" t="s">
         <v>10</v>
       </c>
@@ -3197,7 +3198,7 @@
       </c>
       <c r="D21" s="19"/>
     </row>
-    <row r="22" spans="1:4" ht="16.5">
+    <row r="22" spans="1:4" ht="16">
       <c r="A22" s="21" t="s">
         <v>16</v>
       </c>
@@ -3205,7 +3206,7 @@
       <c r="C22" s="25"/>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" spans="1:4" ht="16.5">
+    <row r="23" spans="1:4" ht="16">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3213,7 +3214,7 @@
       <c r="C23" s="25"/>
       <c r="D23" s="19"/>
     </row>
-    <row r="24" spans="1:4" ht="16.5">
+    <row r="24" spans="1:4" ht="16">
       <c r="A24" s="21" t="s">
         <v>18</v>
       </c>
@@ -3221,7 +3222,7 @@
       <c r="C24" s="25"/>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:4" ht="16.5">
+    <row r="25" spans="1:4" ht="16">
       <c r="A25" s="21" t="s">
         <v>19</v>
       </c>
@@ -3229,7 +3230,7 @@
       <c r="C25" s="25"/>
       <c r="D25" s="19"/>
     </row>
-    <row r="26" spans="1:4" ht="16.5">
+    <row r="26" spans="1:4" ht="16">
       <c r="A26" s="21" t="s">
         <v>20</v>
       </c>
@@ -3237,7 +3238,7 @@
       <c r="C26" s="25"/>
       <c r="D26" s="19"/>
     </row>
-    <row r="27" spans="1:4" ht="16.5">
+    <row r="27" spans="1:4" ht="16">
       <c r="A27" s="21" t="s">
         <v>21</v>
       </c>
@@ -3245,7 +3246,7 @@
       <c r="C27" s="25"/>
       <c r="D27" s="19"/>
     </row>
-    <row r="28" spans="1:4" ht="16.5">
+    <row r="28" spans="1:4" ht="16">
       <c r="A28" s="23" t="s">
         <v>22</v>
       </c>
@@ -3255,7 +3256,7 @@
       </c>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="1:4" ht="16.5">
+    <row r="29" spans="1:4" ht="16">
       <c r="A29" s="23" t="s">
         <v>23</v>
       </c>
@@ -3265,7 +3266,7 @@
       </c>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:4" ht="16.5">
+    <row r="30" spans="1:4" ht="16">
       <c r="A30" s="21" t="s">
         <v>24</v>
       </c>
@@ -3273,7 +3274,7 @@
       <c r="C30" s="25"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:4" ht="16.5">
+    <row r="31" spans="1:4" ht="16">
       <c r="A31" s="21" t="s">
         <v>102</v>
       </c>
@@ -3281,7 +3282,7 @@
       <c r="C31" s="25"/>
       <c r="D31" s="19"/>
     </row>
-    <row r="32" spans="1:4" ht="16.5">
+    <row r="32" spans="1:4" ht="16">
       <c r="A32" s="21" t="s">
         <v>25</v>
       </c>
@@ -3289,7 +3290,7 @@
       <c r="C32" s="25"/>
       <c r="D32" s="19"/>
     </row>
-    <row r="33" spans="1:4" ht="16.5">
+    <row r="33" spans="1:4" ht="16">
       <c r="A33" s="21" t="s">
         <v>105</v>
       </c>
@@ -3297,7 +3298,7 @@
       <c r="C33" s="25"/>
       <c r="D33" s="19"/>
     </row>
-    <row r="34" spans="1:4" ht="16.5">
+    <row r="34" spans="1:4" ht="16">
       <c r="A34" s="21" t="s">
         <v>103</v>
       </c>
@@ -3305,7 +3306,7 @@
       <c r="C34" s="25"/>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="1:4" ht="16.5">
+    <row r="35" spans="1:4" ht="16">
       <c r="A35" s="21" t="s">
         <v>104</v>
       </c>
@@ -3313,7 +3314,7 @@
       <c r="C35" s="25"/>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5">
+    <row r="36" spans="1:4" ht="16">
       <c r="A36" s="28" t="s">
         <v>61</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" ht="15">
       <c r="A40" s="31"/>
       <c r="B40" t="s">
         <v>63</v>
@@ -3337,7 +3338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" ht="15">
       <c r="A41" s="33"/>
       <c r="B41" t="s">
         <v>65</v>
@@ -3346,7 +3347,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" ht="15">
       <c r="A42" s="34"/>
       <c r="B42" t="s">
         <v>66</v>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qtang/Desktop/APM/Git/hc-apm-web/src/src/main/resources/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{094F6CBD-183C-3D4E-93BE-7745BBB488DB}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{9230A461-CBBB-44E5-A05F-3A1F72652729}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="465" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>功能分组</t>
-  </si>
-  <si>
-    <t>设备类型</t>
   </si>
   <si>
     <t>功能等级</t>
@@ -378,10 +375,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>设备类型是否已填写</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>实施必填检查项</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -510,16 +503,22 @@
   <si>
     <t>v2.4</t>
   </si>
+  <si>
+    <t>设备分类</t>
+  </si>
+  <si>
+    <t>设备分类是否已填写</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
-    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="164" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
-    <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
+    <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -1128,7 +1127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
@@ -1152,7 +1151,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1188,7 +1187,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1">
@@ -1215,7 +1214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
@@ -2076,71 +2075,71 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BQ4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="8" width="13.5" style="71" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="8" width="13.44140625" style="71" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.33203125" style="71" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.33203125" style="71" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" style="74" customWidth="1"/>
-    <col min="14" max="14" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" style="74" customWidth="1"/>
+    <col min="14" max="14" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
     <col min="17" max="17" width="19" style="71" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="10" style="71" customWidth="1"/>
-    <col min="20" max="21" width="10.1640625" customWidth="1"/>
-    <col min="22" max="22" width="19.1640625" customWidth="1"/>
-    <col min="23" max="23" width="19.1640625" style="71" customWidth="1"/>
+    <col min="20" max="21" width="10.109375" customWidth="1"/>
+    <col min="22" max="22" width="19.109375" customWidth="1"/>
+    <col min="23" max="23" width="19.109375" style="71" customWidth="1"/>
     <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="10.1640625" customWidth="1"/>
+    <col min="25" max="26" width="10.109375" customWidth="1"/>
     <col min="27" max="27" width="13.6640625" customWidth="1"/>
-    <col min="28" max="28" width="17.5" customWidth="1"/>
-    <col min="29" max="29" width="14.5" customWidth="1"/>
-    <col min="30" max="30" width="11.1640625" customWidth="1"/>
+    <col min="28" max="28" width="17.44140625" customWidth="1"/>
+    <col min="29" max="29" width="14.44140625" customWidth="1"/>
+    <col min="30" max="30" width="11.109375" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
-    <col min="33" max="33" width="10.1640625" customWidth="1"/>
-    <col min="34" max="34" width="11.5" customWidth="1"/>
-    <col min="35" max="35" width="11.5" style="71" customWidth="1"/>
-    <col min="36" max="36" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" customWidth="1"/>
+    <col min="33" max="33" width="10.109375" customWidth="1"/>
+    <col min="34" max="34" width="11.44140625" customWidth="1"/>
+    <col min="35" max="35" width="11.44140625" style="71" customWidth="1"/>
+    <col min="36" max="36" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.33203125" customWidth="1"/>
     <col min="38" max="38" width="14.6640625" customWidth="1"/>
-    <col min="39" max="39" width="12.5" customWidth="1"/>
+    <col min="39" max="39" width="12.44140625" customWidth="1"/>
     <col min="40" max="40" width="12.6640625" customWidth="1"/>
     <col min="41" max="42" width="12.33203125" style="74" customWidth="1"/>
-    <col min="43" max="43" width="16.1640625" style="74" customWidth="1"/>
-    <col min="44" max="44" width="12.83203125" style="74" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.1640625" style="74" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.1640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.109375" style="74" customWidth="1"/>
+    <col min="44" max="44" width="12.77734375" style="74" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.109375" style="74" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="11.6640625" customWidth="1"/>
-    <col min="53" max="54" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="11.33203125" customWidth="1"/>
     <col min="56" max="57" width="11.33203125" style="71" customWidth="1"/>
-    <col min="58" max="58" width="27.5" customWidth="1"/>
-    <col min="59" max="59" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="27.44140625" customWidth="1"/>
+    <col min="59" max="59" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69" ht="27" hidden="1" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="76"/>
       <c r="F1" s="76"/>
@@ -2153,17 +2152,17 @@
       <c r="M1" s="76"/>
       <c r="BG1" s="76"/>
     </row>
-    <row r="2" spans="1:69" ht="14">
+    <row r="2" spans="1:69" ht="15.75">
       <c r="A2" s="77"/>
       <c r="B2" s="79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" s="76"/>
       <c r="E2" s="78" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F2" s="76"/>
       <c r="G2" s="76"/>
@@ -2175,7 +2174,7 @@
       <c r="M2" s="76"/>
       <c r="BG2" s="76"/>
     </row>
-    <row r="3" spans="1:69" ht="34" thickBot="1">
+    <row r="3" spans="1:69" ht="33.75" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2248,7 +2247,7 @@
       <c r="BP3" s="72"/>
       <c r="BQ3" s="72"/>
     </row>
-    <row r="4" spans="1:69" ht="14">
+    <row r="4" spans="1:69" ht="15.75">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2299,12 +2298,12 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" thickBot="1">
+    <row r="1" spans="1:1" ht="33.75" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -2342,14 +2341,14 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="4" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" thickBot="1">
+    <row r="1" spans="1:5" ht="33.75" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -2377,10 +2376,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2394,10 +2393,10 @@
         <v>18900000000</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2411,10 +2410,10 @@
         <v>18911111111</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2648,314 +2647,314 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="35" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="35"/>
-    <col min="4" max="4" width="27.83203125" style="35" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="35"/>
+    <col min="3" max="3" width="8.77734375" style="35"/>
+    <col min="4" max="4" width="27.77734375" style="35" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1">
       <c r="A1" s="81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
       <c r="D1" s="81"/>
     </row>
-    <row r="2" spans="1:4" ht="18" thickBot="1">
+    <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="C2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="D2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17">
+    </row>
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="38">
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="41" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" thickBot="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1">
       <c r="A4" s="42">
         <v>2</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" thickBot="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1">
       <c r="A5" s="42">
         <v>3</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="C5" s="44"/>
       <c r="D5" s="45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
       <c r="A6" s="46"/>
       <c r="B6" s="47"/>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
     </row>
-    <row r="7" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+    <row r="7" spans="1:4" s="49" customFormat="1" ht="16.5" thickBot="1">
       <c r="A7" s="82" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="83"/>
       <c r="C7" s="83"/>
       <c r="D7" s="84"/>
     </row>
-    <row r="8" spans="1:4" s="49" customFormat="1" ht="18" thickBot="1">
+    <row r="8" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
       <c r="A8" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="C8" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="D8" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="51" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="17">
+    </row>
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="52">
         <v>3</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="55"/>
     </row>
-    <row r="10" spans="1:4" ht="17">
+    <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="38">
         <v>4</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="57"/>
     </row>
-    <row r="11" spans="1:4" ht="18" thickBot="1">
+    <row r="11" spans="1:4" ht="17.25" thickBot="1">
       <c r="A11" s="38">
         <v>5</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="57"/>
     </row>
-    <row r="12" spans="1:4" ht="17">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="52">
         <v>6</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="57"/>
     </row>
-    <row r="13" spans="1:4" ht="17">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="38">
         <v>7</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="56"/>
       <c r="D13" s="57"/>
     </row>
-    <row r="14" spans="1:4" ht="18" thickBot="1">
+    <row r="14" spans="1:4" ht="17.25" thickBot="1">
       <c r="A14" s="38">
         <v>8</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="57"/>
     </row>
-    <row r="15" spans="1:4" ht="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="52">
         <v>9</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="57"/>
     </row>
-    <row r="16" spans="1:4" ht="17">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="38">
         <v>10</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" s="56"/>
       <c r="D16" s="57"/>
     </row>
-    <row r="17" spans="1:4" ht="18" thickBot="1">
+    <row r="17" spans="1:4" ht="17.25" thickBot="1">
       <c r="A17" s="38">
         <v>11</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="52">
         <v>12</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="57"/>
     </row>
-    <row r="19" spans="1:4" ht="17">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="38">
         <v>13</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C19" s="56"/>
       <c r="D19" s="57"/>
     </row>
-    <row r="20" spans="1:4" ht="18" thickBot="1">
+    <row r="20" spans="1:4" ht="17.25" thickBot="1">
       <c r="A20" s="38">
         <v>14</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" s="56"/>
       <c r="D20" s="57"/>
     </row>
-    <row r="21" spans="1:4" ht="17">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="52">
         <v>15</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="56"/>
       <c r="D21" s="57"/>
     </row>
-    <row r="22" spans="1:4" ht="18" thickBot="1">
+    <row r="22" spans="1:4" ht="17.25" thickBot="1">
       <c r="A22" s="38">
         <v>16</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="58"/>
       <c r="D22" s="59"/>
     </row>
-    <row r="23" spans="1:4" ht="16" thickBot="1">
+    <row r="23" spans="1:4" ht="16.5" thickBot="1">
       <c r="A23" s="60"/>
     </row>
-    <row r="24" spans="1:4" ht="18" thickBot="1">
+    <row r="24" spans="1:4" ht="16.5" thickBot="1">
       <c r="A24" s="85" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B24" s="86"/>
       <c r="C24" s="86"/>
       <c r="D24" s="87"/>
     </row>
-    <row r="25" spans="1:4" ht="18" thickBot="1">
+    <row r="25" spans="1:4" ht="17.25" thickBot="1">
       <c r="A25" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="C25" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="D25" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="62" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" thickBot="1">
+    </row>
+    <row r="26" spans="1:4" ht="16.5" thickBot="1">
       <c r="A26" s="38">
         <v>17</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" s="64"/>
       <c r="D26" s="65" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="16" thickBot="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" thickBot="1">
       <c r="A27" s="38">
         <v>18</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="41" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="38">
         <v>19</v>
       </c>
       <c r="B28" s="63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" s="66"/>
       <c r="D28" s="67" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16" thickBot="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16.5" thickBot="1">
       <c r="A29" s="38">
         <v>20</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="69"/>
       <c r="D29" s="70" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2980,61 +2979,61 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.5" style="30" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="30" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="88" t="s">
         <v>42</v>
-      </c>
-      <c r="B1" s="88" t="s">
-        <v>43</v>
       </c>
       <c r="C1" s="88"/>
       <c r="D1" s="88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="88"/>
       <c r="B2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="88"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.5">
+      <c r="A3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="88"/>
-    </row>
-    <row r="3" spans="1:4" ht="16">
-      <c r="A3" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>47</v>
-      </c>
       <c r="D3" s="19"/>
     </row>
-    <row r="4" spans="1:4" ht="16">
+    <row r="4" spans="1:4" ht="16.5">
       <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="19"/>
     </row>
-    <row r="5" spans="1:4" ht="16">
+    <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="21" t="s">
         <v>13</v>
       </c>
@@ -3042,59 +3041,59 @@
       <c r="C5" s="22"/>
       <c r="D5" s="19"/>
     </row>
-    <row r="6" spans="1:4" ht="16">
+    <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="16.5">
+      <c r="A7" s="21" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16">
-      <c r="A7" s="21" t="s">
-        <v>52</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
       <c r="D7" s="19"/>
     </row>
-    <row r="8" spans="1:4" ht="16">
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="19"/>
     </row>
-    <row r="9" spans="1:4" ht="16">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="26" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="27" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="16.5">
+      <c r="A10" s="23" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16">
-      <c r="A10" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="19"/>
     </row>
-    <row r="11" spans="1:4" ht="16">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="21" t="s">
         <v>15</v>
       </c>
@@ -3102,103 +3101,103 @@
       <c r="C11" s="25"/>
       <c r="D11" s="19"/>
     </row>
-    <row r="12" spans="1:4" ht="16">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="23" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" ht="16">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="1:4" ht="16.5">
+      <c r="A14" s="21" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" spans="1:4" ht="16">
-      <c r="A14" s="21" t="s">
-        <v>29</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
       <c r="D14" s="19"/>
     </row>
-    <row r="15" spans="1:4" ht="16">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="19"/>
     </row>
-    <row r="16" spans="1:4" ht="16">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
       <c r="D16" s="19"/>
     </row>
-    <row r="17" spans="1:4" ht="16">
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="19"/>
     </row>
-    <row r="18" spans="1:4" ht="16">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="19"/>
     </row>
-    <row r="19" spans="1:4" ht="16">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
       <c r="D19" s="19"/>
     </row>
-    <row r="20" spans="1:4" ht="16">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" s="19"/>
     </row>
-    <row r="21" spans="1:4" ht="16">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="19"/>
     </row>
-    <row r="22" spans="1:4" ht="16">
+    <row r="22" spans="1:4" ht="16.5">
       <c r="A22" s="21" t="s">
         <v>16</v>
       </c>
@@ -3206,7 +3205,7 @@
       <c r="C22" s="25"/>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" spans="1:4" ht="16">
+    <row r="23" spans="1:4" ht="16.5">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3214,7 +3213,7 @@
       <c r="C23" s="25"/>
       <c r="D23" s="19"/>
     </row>
-    <row r="24" spans="1:4" ht="16">
+    <row r="24" spans="1:4" ht="16.5">
       <c r="A24" s="21" t="s">
         <v>18</v>
       </c>
@@ -3222,7 +3221,7 @@
       <c r="C24" s="25"/>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:4" ht="16">
+    <row r="25" spans="1:4" ht="16.5">
       <c r="A25" s="21" t="s">
         <v>19</v>
       </c>
@@ -3230,7 +3229,7 @@
       <c r="C25" s="25"/>
       <c r="D25" s="19"/>
     </row>
-    <row r="26" spans="1:4" ht="16">
+    <row r="26" spans="1:4" ht="16.5">
       <c r="A26" s="21" t="s">
         <v>20</v>
       </c>
@@ -3238,7 +3237,7 @@
       <c r="C26" s="25"/>
       <c r="D26" s="19"/>
     </row>
-    <row r="27" spans="1:4" ht="16">
+    <row r="27" spans="1:4" ht="16.5">
       <c r="A27" s="21" t="s">
         <v>21</v>
       </c>
@@ -3246,27 +3245,27 @@
       <c r="C27" s="25"/>
       <c r="D27" s="19"/>
     </row>
-    <row r="28" spans="1:4" ht="16">
+    <row r="28" spans="1:4" ht="16.5">
       <c r="A28" s="23" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="1:4" ht="16">
+    <row r="29" spans="1:4" ht="16.5">
       <c r="A29" s="23" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:4" ht="16">
+    <row r="30" spans="1:4" ht="16.5">
       <c r="A30" s="21" t="s">
         <v>24</v>
       </c>
@@ -3274,15 +3273,15 @@
       <c r="C30" s="25"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:4" ht="16">
+    <row r="31" spans="1:4" ht="16.5">
       <c r="A31" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
       <c r="D31" s="19"/>
     </row>
-    <row r="32" spans="1:4" ht="16">
+    <row r="32" spans="1:4" ht="16.5">
       <c r="A32" s="21" t="s">
         <v>25</v>
       </c>
@@ -3290,70 +3289,70 @@
       <c r="C32" s="25"/>
       <c r="D32" s="19"/>
     </row>
-    <row r="33" spans="1:4" ht="16">
+    <row r="33" spans="1:4" ht="16.5">
       <c r="A33" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
       <c r="D33" s="19"/>
     </row>
-    <row r="34" spans="1:4" ht="16">
+    <row r="34" spans="1:4" ht="16.5">
       <c r="A34" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="1:4" ht="16">
+    <row r="35" spans="1:4" ht="16.5">
       <c r="A35" s="21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="1:4" ht="16">
+    <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D36" s="19"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="31"/>
       <c r="B40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15">
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="33"/>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="34"/>
       <c r="B42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="32" t="s">
         <v>66</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503282840\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589B05AE-838F-4552-B2B4-C9141286F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D0C098-A30D-45CC-A3AC-E985C8152560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
     <sheet name="Org List" sheetId="11" r:id="rId2"/>
     <sheet name="User List" sheetId="9" state="hidden" r:id="rId3"/>
-    <sheet name="TCM List" sheetId="16" r:id="rId4"/>
+    <sheet name="TCM List" sheetId="17" r:id="rId4"/>
     <sheet name="必填字段检查表" sheetId="15" r:id="rId5"/>
     <sheet name="必填字段填写说明" sheetId="14" r:id="rId6"/>
   </sheets>
@@ -1951,7 +1951,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54DBCEA2-E63B-482D-81E6-842730163ED2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D98556DB-1D7C-416D-99D3-37A601589D60}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2842,7 +2842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3F9B3B-4A14-44F0-81B5-D3A5301EA0D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFD2668-6E96-4E8D-A1DF-161B65DF74EE}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
@@ -2872,7 +2872,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{09AA6B66-E490-4CE5-AC2A-D8C0E3AA8ECF}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{7A0652C7-473A-4F8D-8A9E-030D4833B8D1}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503282840\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D0C098-A30D-45CC-A3AC-E985C8152560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589B05AE-838F-4552-B2B4-C9141286F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
     <sheet name="Org List" sheetId="11" r:id="rId2"/>
     <sheet name="User List" sheetId="9" state="hidden" r:id="rId3"/>
-    <sheet name="TCM List" sheetId="17" r:id="rId4"/>
+    <sheet name="TCM List" sheetId="16" r:id="rId4"/>
     <sheet name="必填字段检查表" sheetId="15" r:id="rId5"/>
     <sheet name="必填字段填写说明" sheetId="14" r:id="rId6"/>
   </sheets>
@@ -1951,7 +1951,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D98556DB-1D7C-416D-99D3-37A601589D60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54DBCEA2-E63B-482D-81E6-842730163ED2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2842,7 +2842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFD2668-6E96-4E8D-A1DF-161B65DF74EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3F9B3B-4A14-44F0-81B5-D3A5301EA0D4}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
@@ -2872,7 +2872,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{7A0652C7-473A-4F8D-8A9E-030D4833B8D1}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{09AA6B66-E490-4CE5-AC2A-D8C0E3AA8ECF}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -1,28 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503282840\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\temp3\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D0C098-A30D-45CC-A3AC-E985C8152560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD001E8-AD43-4AD5-9A11-BDAF96800553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
-    <sheet name="Org List" sheetId="11" r:id="rId2"/>
+    <sheet name="Org List" sheetId="18" r:id="rId2"/>
     <sheet name="User List" sheetId="9" state="hidden" r:id="rId3"/>
-    <sheet name="TCM List" sheetId="17" r:id="rId4"/>
+    <sheet name="TCM List" sheetId="19" r:id="rId4"/>
     <sheet name="必填字段检查表" sheetId="15" r:id="rId5"/>
     <sheet name="必填字段填写说明" sheetId="14" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Org List'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'TCM List'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'User List'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -62,10 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
-  <si>
-    <t>设备列表</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
   <si>
     <t>人员列表</t>
   </si>
@@ -73,9 +68,6 @@
     <t>部门列表</t>
   </si>
   <si>
-    <t>部门名称</t>
-  </si>
-  <si>
     <t>人员编号</t>
   </si>
   <si>
@@ -88,21 +80,12 @@
     <t>李四</t>
   </si>
   <si>
-    <t>总价值</t>
-  </si>
-  <si>
-    <t>总数量</t>
-  </si>
-  <si>
     <t>采购价格</t>
   </si>
   <si>
     <t>设备名称</t>
   </si>
   <si>
-    <t>医院代号</t>
-  </si>
-  <si>
     <t>设备别名</t>
   </si>
   <si>
@@ -163,9 +146,6 @@
     <t>IT系统编号</t>
   </si>
   <si>
-    <t>医院名称</t>
-  </si>
-  <si>
     <t>设备编号</t>
   </si>
   <si>
@@ -182,10 +162,6 @@
   </si>
   <si>
     <t>设备科</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-所有日期格式为MM/DD/YYYY</t>
   </si>
   <si>
     <t>字段</t>
@@ -473,24 +449,6 @@
     <t>必须有有效数据且院区不重复</t>
   </si>
   <si>
-    <r>
-      <t>所有日期格式为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Franklin Gothic Medium"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MM/DD/YYYY</t>
-    </r>
-  </si>
-  <si>
-    <t>模版文件版本号</t>
-  </si>
-  <si>
     <t>上次保养日期</t>
   </si>
   <si>
@@ -503,9 +461,6 @@
     <t>上次巡检日期</t>
   </si>
   <si>
-    <t>v2.4</t>
-  </si>
-  <si>
     <t>设备分类</t>
   </si>
   <si>
@@ -513,22 +468,18 @@
   </si>
   <si>
     <t>中医诊疗设备分类列表</t>
-  </si>
-  <si>
-    <t>分类名称</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="165" formatCode="&quot;Reorder&quot;;&quot;&quot;;&quot;&quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;&quot;;&quot;&quot;;&quot;Clear Pick List Selected in B2&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$¥-804]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="3" tint="0.14993743705557422"/>
@@ -637,27 +588,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="3" tint="0.14993743705557422"/>
-      <name val="Franklin Gothic Medium"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="3" tint="0.14993743705557422"/>
-      <name val="Franklin Gothic Medium"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Franklin Gothic Medium"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Franklin Gothic Medium"/>
       <family val="3"/>
@@ -774,24 +704,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Franklin Gothic Medium"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="3" tint="0.14993743705557422"/>
-      <name val="Franklin Gothic Medium"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,18 +715,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -876,15 +778,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1130,6 +1023,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1169,16 +1071,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="12"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="12" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1195,226 +1095,194 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFill="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="3" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="4" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="3" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="15"/>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="15" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="16" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="15" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="15" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="15" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="15" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="15" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="15" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="5" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="12" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="14" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="13" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1436,25 +1304,7 @@
     <cellStyle name="链接单元格" xfId="8" builtinId="24" customBuiltin="1"/>
     <cellStyle name="已访问的超链接" xfId="2" builtinId="9" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <b/>
@@ -1526,14 +1376,14 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Warehouse Inventory" defaultPivotStyle="PivotStyleMedium2">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
     </tableStyle>
     <tableStyle name="Warehouse Inventory" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="lastColumn" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1548,292 +1398,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>689229</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>209549</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>772414</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Inventory List" descr="Navigation shape to view the Inventory Pick List">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Select to view Inventory Pick List worksheet"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2213229" y="409574"/>
-          <a:ext cx="1711960" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:effectLst/>
-        <a:scene3d>
-          <a:camera prst="orthographicFront">
-            <a:rot lat="0" lon="0" rev="0"/>
-          </a:camera>
-          <a:lightRig rig="threePt" dir="t">
-            <a:rot lat="0" lon="0" rev="1200000"/>
-          </a:lightRig>
-        </a:scene3d>
-        <a:sp3d/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>部门列表</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fPrintsWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>816610</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>409575</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Inventory List" descr="Navigation shape to view the Inventory Pick List">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2" tooltip="Select to view Inventory Pick List worksheet"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C1A07A5-FB8A-40BE-83CE-10D7D4C99915}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4105275" y="381000"/>
-          <a:ext cx="1711960" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:effectLst/>
-        <a:scene3d>
-          <a:camera prst="orthographicFront">
-            <a:rot lat="0" lon="0" rev="0"/>
-          </a:camera>
-          <a:lightRig rig="threePt" dir="t">
-            <a:rot lat="0" lon="0" rev="1200000"/>
-          </a:lightRig>
-        </a:scene3d>
-        <a:sp3d/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>中医诊疗设备分类列表</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fPrintsWithSheet="0"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3809</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Inventory List" descr="Select to view Inventory List">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="19049" y="514350"/>
-          <a:ext cx="1737360" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:effectLst/>
-        <a:scene3d>
-          <a:camera prst="orthographicFront">
-            <a:rot lat="0" lon="0" rev="0"/>
-          </a:camera>
-          <a:lightRig rig="threePt" dir="t">
-            <a:rot lat="0" lon="0" rev="1200000"/>
-          </a:lightRig>
-        </a:scene3d>
-        <a:sp3d/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>设备列表</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fPrintsWithSheet="0"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1864,103 +1428,6 @@
         <a:xfrm flipH="1">
           <a:off x="19050" y="523875"/>
           <a:ext cx="1737360" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:effectLst/>
-        <a:scene3d>
-          <a:camera prst="orthographicFront">
-            <a:rot lat="0" lon="0" rev="0"/>
-          </a:camera>
-          <a:lightRig rig="threePt" dir="t">
-            <a:rot lat="0" lon="0" rev="1200000"/>
-          </a:lightRig>
-        </a:scene3d>
-        <a:sp3d/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>设备列表</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fPrintsWithSheet="0"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3809</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Inventory List" descr="Select to view Inventory List">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" tooltip="Click to view the Warehouse Inventory List"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D98556DB-1D7C-416D-99D3-37A601589D60}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="19049" y="514350"/>
-          <a:ext cx="1765935" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst/>
@@ -2268,266 +1735,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="shtInventoryList">
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="0.59999389629810485"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BQ4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="F1:BE1"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="17.76953125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="8" width="13.44140625" style="71" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" style="71" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="71" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" customWidth="1"/>
-    <col min="13" max="13" width="18.77734375" style="74" customWidth="1"/>
-    <col min="14" max="14" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" customWidth="1"/>
+    <col min="6" max="8" width="13.453125" style="66" customWidth="1"/>
+    <col min="9" max="9" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.31640625" style="66" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.31640625" style="66" customWidth="1"/>
+    <col min="12" max="12" width="9.08984375" customWidth="1"/>
+    <col min="13" max="13" width="18.76953125" style="67" customWidth="1"/>
+    <col min="14" max="14" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.6796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="19" style="71" customWidth="1"/>
+    <col min="17" max="17" width="19" style="66" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="10" style="71" customWidth="1"/>
-    <col min="20" max="21" width="10.109375" customWidth="1"/>
-    <col min="22" max="22" width="19.109375" customWidth="1"/>
-    <col min="23" max="23" width="19.109375" style="71" customWidth="1"/>
-    <col min="24" max="24" width="14.6640625" customWidth="1"/>
-    <col min="25" max="26" width="10.109375" customWidth="1"/>
-    <col min="27" max="27" width="13.6640625" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" customWidth="1"/>
-    <col min="29" max="29" width="14.44140625" customWidth="1"/>
-    <col min="30" max="30" width="11.109375" customWidth="1"/>
+    <col min="19" max="19" width="10" style="66" customWidth="1"/>
+    <col min="20" max="21" width="10.08984375" customWidth="1"/>
+    <col min="22" max="22" width="19.08984375" customWidth="1"/>
+    <col min="23" max="23" width="19.08984375" style="66" customWidth="1"/>
+    <col min="24" max="24" width="14.6796875" customWidth="1"/>
+    <col min="25" max="26" width="10.08984375" customWidth="1"/>
+    <col min="27" max="27" width="13.6796875" customWidth="1"/>
+    <col min="28" max="28" width="17.453125" customWidth="1"/>
+    <col min="29" max="29" width="14.453125" customWidth="1"/>
+    <col min="30" max="30" width="11.08984375" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" customWidth="1"/>
-    <col min="33" max="33" width="10.109375" customWidth="1"/>
-    <col min="34" max="34" width="11.44140625" customWidth="1"/>
-    <col min="35" max="35" width="11.44140625" style="71" customWidth="1"/>
-    <col min="36" max="36" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.33203125" customWidth="1"/>
-    <col min="38" max="38" width="14.6640625" customWidth="1"/>
-    <col min="39" max="39" width="12.44140625" customWidth="1"/>
-    <col min="40" max="40" width="12.6640625" customWidth="1"/>
-    <col min="41" max="42" width="12.33203125" style="74" customWidth="1"/>
-    <col min="43" max="43" width="16.109375" style="74" customWidth="1"/>
-    <col min="44" max="44" width="12.77734375" style="74" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.6640625" customWidth="1"/>
-    <col min="53" max="54" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.33203125" customWidth="1"/>
-    <col min="56" max="57" width="11.33203125" style="71" customWidth="1"/>
-    <col min="58" max="58" width="27.44140625" customWidth="1"/>
-    <col min="59" max="59" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.453125" customWidth="1"/>
+    <col min="33" max="33" width="10.08984375" customWidth="1"/>
+    <col min="34" max="34" width="11.453125" customWidth="1"/>
+    <col min="35" max="35" width="11.453125" style="66" customWidth="1"/>
+    <col min="36" max="36" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.31640625" customWidth="1"/>
+    <col min="38" max="38" width="14.6796875" customWidth="1"/>
+    <col min="39" max="39" width="12.453125" customWidth="1"/>
+    <col min="40" max="40" width="12.6796875" customWidth="1"/>
+    <col min="41" max="42" width="12.31640625" style="67" customWidth="1"/>
+    <col min="43" max="43" width="16.08984375" style="67" customWidth="1"/>
+    <col min="44" max="44" width="12.76953125" style="67" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.08984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.08984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.08984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.31640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.6796875" customWidth="1"/>
+    <col min="53" max="54" width="12.76953125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.31640625" customWidth="1"/>
+    <col min="56" max="57" width="11.31640625" style="66" customWidth="1"/>
+    <col min="58" max="58" width="27.453125" customWidth="1"/>
+    <col min="59" max="59" width="10.76953125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.6796875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="12.31640625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:69" ht="27" hidden="1" customHeight="1">
-      <c r="A1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="75" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="BG1" s="76"/>
-    </row>
-    <row r="2" spans="1:69" ht="15.75">
-      <c r="A2" s="77"/>
-      <c r="B2" s="79" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="BG2" s="76"/>
-    </row>
-    <row r="3" spans="1:69" ht="33.75" thickBot="1">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="1"/>
-      <c r="AM3" s="1"/>
-      <c r="AN3" s="1"/>
-      <c r="AO3" s="73"/>
-      <c r="AP3" s="73"/>
-      <c r="AQ3" s="73"/>
-      <c r="AR3" s="73"/>
-      <c r="AS3" s="73"/>
-      <c r="AT3" s="73"/>
-      <c r="AU3" s="73"/>
-      <c r="AV3" s="1"/>
-      <c r="AW3" s="1"/>
-      <c r="AX3" s="1"/>
-      <c r="AY3" s="1"/>
-      <c r="AZ3" s="1"/>
-      <c r="BA3" s="1"/>
-      <c r="BB3" s="1"/>
-      <c r="BC3" s="72"/>
-      <c r="BD3" s="72"/>
-      <c r="BE3" s="72"/>
-      <c r="BF3" s="72"/>
-      <c r="BG3" s="1"/>
-      <c r="BH3" s="72"/>
-      <c r="BI3" s="72"/>
-      <c r="BJ3" s="72"/>
-      <c r="BK3" s="72"/>
-      <c r="BL3" s="72"/>
-      <c r="BM3" s="72"/>
-      <c r="BN3" s="72"/>
-      <c r="BO3" s="72"/>
-      <c r="BP3" s="72"/>
-      <c r="BQ3" s="72"/>
-    </row>
-    <row r="4" spans="1:69" ht="15.75">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="BG4" s="8"/>
-      <c r="BH4" s="8"/>
-      <c r="BI4" s="8"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="D1 E4:H4">
-    <cfRule type="expression" dxfId="4" priority="85">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="3" priority="58">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="2" priority="37">
-      <formula>"If(blnBinNo=""True"")"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <sheetData/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="66" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="shtPickList">
-    <tabColor theme="4" tint="0.39997558519241921"/>
-    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF2814F-2C7A-40AA-B80B-26D0885DFA4D}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.75" thickBot="1">
-      <c r="A1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="11"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="80" t="s">
-        <v>3</v>
+    <row r="1" spans="1:1" ht="34.799999999999997" thickBot="1">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations xWindow="567" yWindow="330" count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter differentFirst="1">
-    <oddFooter>Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2538,289 +1832,289 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.76953125" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="4" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.75" thickBot="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
+    <row r="1" spans="1:5" ht="34.799999999999997" thickBot="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8"/>
+      <c r="A2" s="6"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>18900000000</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="10">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10">
-        <v>18900000000</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="B6" s="8">
         <v>2</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>18911111111</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>38</v>
+      <c r="D6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <dataValidations xWindow="144" yWindow="400" count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Navigation link to Warehouse Inventory List worksheet" sqref="A2" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D8" xr:uid="{00000000-0002-0000-0200-000001000000}">
@@ -2842,359 +2136,337 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFD2668-6E96-4E8D-A1DF-161B65DF74EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9215DBD-E3F6-4289-AC14-E8DC44626F3D}">
   <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
+    <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="71" customWidth="1"/>
-    <col min="2" max="16384" width="8.77734375" style="71"/>
+    <col min="1" max="1" width="40.04296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.75" thickBot="1">
-      <c r="A1" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="11"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="80" t="s">
-        <v>108</v>
+    <row r="1" spans="1:1" ht="34.5">
+      <c r="A1" s="68" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="To clear the pick list table in this worksheet, activate the object in B2 or press ALT+F8 and type &quot;ClearPickList&quot; with no spaces, then select RUN" sqref="A2" xr:uid="{7A0652C7-473A-4F8D-8A9E-030D4833B8D1}"/>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter differentFirst="1">
-    <oddFooter>Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="35" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="35"/>
-    <col min="4" max="4" width="27.77734375" style="35" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="35"/>
+    <col min="1" max="1" width="8.76953125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="32.6796875" style="30" customWidth="1"/>
+    <col min="3" max="3" width="8.76953125" style="30"/>
+    <col min="4" max="4" width="27.76953125" style="30" customWidth="1"/>
+    <col min="5" max="16384" width="8.76953125" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A2" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.3">
+      <c r="A3" s="33">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A4" s="37">
+        <v>2</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A5" s="37">
+        <v>3</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="44" customFormat="1" ht="15.6" thickBot="1">
+      <c r="A6" s="41"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+    </row>
+    <row r="7" spans="1:4" s="44" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A7" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A2" s="36" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="72"/>
+    </row>
+    <row r="8" spans="1:4" s="44" customFormat="1" ht="15.6" thickBot="1">
+      <c r="A8" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.3">
+      <c r="A9" s="47">
+        <v>3</v>
+      </c>
+      <c r="B9" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.3">
+      <c r="A10" s="33">
+        <v>4</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C10" s="51"/>
+      <c r="D10" s="52"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A11" s="33">
+        <v>5</v>
+      </c>
+      <c r="B11" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.3">
+      <c r="A12" s="47">
+        <v>6</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5">
-      <c r="A3" s="38">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A4" s="42">
-        <v>2</v>
-      </c>
-      <c r="B4" s="43" t="s">
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.3">
+      <c r="A13" s="33">
+        <v>7</v>
+      </c>
+      <c r="B13" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="45" t="s">
+      <c r="C13" s="51"/>
+      <c r="D13" s="52"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A14" s="33">
+        <v>8</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A5" s="42">
-        <v>3</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-    </row>
-    <row r="7" spans="1:4" s="49" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A7" s="82" t="s">
+      <c r="C14" s="51"/>
+      <c r="D14" s="52"/>
+    </row>
+    <row r="15" spans="1:4" ht="14.4">
+      <c r="A15" s="47">
+        <v>9</v>
+      </c>
+      <c r="B15" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="84"/>
-    </row>
-    <row r="8" spans="1:4" s="49" customFormat="1" ht="17.25" thickBot="1">
-      <c r="A8" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="52">
-        <v>3</v>
-      </c>
-      <c r="B9" s="53" t="s">
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.3">
+      <c r="A16" s="33">
+        <v>10</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="55"/>
-    </row>
-    <row r="10" spans="1:4" ht="16.5">
-      <c r="A10" s="38">
-        <v>4</v>
-      </c>
-      <c r="B10" s="39" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A17" s="33">
+        <v>11</v>
+      </c>
+      <c r="B17" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="57"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A11" s="38">
-        <v>5</v>
-      </c>
-      <c r="B11" s="39" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="57"/>
-    </row>
-    <row r="12" spans="1:4" ht="16.5">
-      <c r="A12" s="52">
-        <v>6</v>
-      </c>
-      <c r="B12" s="39" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="15.3">
+      <c r="A18" s="47">
+        <v>12</v>
+      </c>
+      <c r="B18" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="57"/>
-    </row>
-    <row r="13" spans="1:4" ht="16.5">
-      <c r="A13" s="38">
-        <v>7</v>
-      </c>
-      <c r="B13" s="39" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.3">
+      <c r="A19" s="33">
+        <v>13</v>
+      </c>
+      <c r="B19" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-    </row>
-    <row r="14" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A14" s="38">
-        <v>8</v>
-      </c>
-      <c r="B14" s="39" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A20" s="33">
+        <v>14</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="52">
-        <v>9</v>
-      </c>
-      <c r="B15" s="56" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.3">
+      <c r="A21" s="47">
+        <v>15</v>
+      </c>
+      <c r="B21" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="57"/>
-    </row>
-    <row r="16" spans="1:4" ht="16.5">
-      <c r="A16" s="38">
-        <v>10</v>
-      </c>
-      <c r="B16" s="39" t="s">
+      <c r="C21" s="51"/>
+      <c r="D21" s="52"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A22" s="33">
+        <v>16</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="57"/>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A17" s="38">
-        <v>11</v>
-      </c>
-      <c r="B17" s="39" t="s">
+      <c r="C22" s="53"/>
+      <c r="D22" s="54"/>
+    </row>
+    <row r="23" spans="1:4" ht="14.7" thickBot="1">
+      <c r="A23" s="55"/>
+    </row>
+    <row r="24" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A24" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57" t="s">
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" thickBot="1">
+      <c r="A25" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.7" thickBot="1">
+      <c r="A26" s="33">
+        <v>17</v>
+      </c>
+      <c r="B26" s="58" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5">
-      <c r="A18" s="52">
-        <v>12</v>
-      </c>
-      <c r="B18" s="39" t="s">
+      <c r="C26" s="59"/>
+      <c r="D26" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-    </row>
-    <row r="19" spans="1:4" ht="16.5">
-      <c r="A19" s="38">
-        <v>13</v>
-      </c>
-      <c r="B19" s="39" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="14.7" thickBot="1">
+      <c r="A27" s="33">
+        <v>18</v>
+      </c>
+      <c r="B27" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="57"/>
-    </row>
-    <row r="20" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A20" s="38">
-        <v>14</v>
-      </c>
-      <c r="B20" s="39" t="s">
+      <c r="C27" s="35"/>
+      <c r="D27" s="36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.4">
+      <c r="A28" s="33">
+        <v>19</v>
+      </c>
+      <c r="B28" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="57"/>
-    </row>
-    <row r="21" spans="1:4" ht="16.5">
-      <c r="A21" s="52">
-        <v>15</v>
-      </c>
-      <c r="B21" s="39" t="s">
+      <c r="C28" s="61"/>
+      <c r="D28" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-    </row>
-    <row r="22" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A22" s="38">
-        <v>16</v>
-      </c>
-      <c r="B22" s="43" t="s">
+    </row>
+    <row r="29" spans="1:4" ht="14.7" thickBot="1">
+      <c r="A29" s="33">
+        <v>20</v>
+      </c>
+      <c r="B29" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="59"/>
-    </row>
-    <row r="23" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A23" s="60"/>
-    </row>
-    <row r="24" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A24" s="85" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
-    </row>
-    <row r="25" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A25" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="62" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="62" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A26" s="38">
-        <v>17</v>
-      </c>
-      <c r="B26" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A27" s="38">
-        <v>18</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="38">
-        <v>19</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A29" s="38">
-        <v>20</v>
-      </c>
-      <c r="B29" s="68" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="69"/>
-      <c r="D29" s="70" t="s">
-        <v>95</v>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3203,7 +2475,7 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A24:D24"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C22 C26:C29 C3:C5" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Y,N"</formula1>
@@ -3219,380 +2491,380 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="12.6796875" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="76"/>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="76"/>
+    </row>
+    <row r="3" spans="1:4" ht="15">
+      <c r="A3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" spans="1:4" ht="15">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="15">
+      <c r="A6" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="88" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88" t="s">
+      <c r="D6" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="88"/>
-      <c r="B2" s="16" t="s">
+    <row r="7" spans="1:4" ht="15">
+      <c r="A7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:4" ht="15">
+      <c r="A8" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="88"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.5">
-      <c r="A3" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="15">
+      <c r="A9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="4" spans="1:4" ht="16.5">
-      <c r="A4" s="17" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="A10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:4" ht="15">
+      <c r="A11" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4" ht="15">
+      <c r="A12" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:4" ht="15">
+      <c r="A13" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" spans="1:4" ht="15">
+      <c r="A14" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" ht="15">
+      <c r="A15" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" ht="15">
+      <c r="A16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" ht="15">
+      <c r="A17" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" ht="15">
+      <c r="A18" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" ht="15">
+      <c r="A19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="15">
+      <c r="A20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="15">
+      <c r="A21" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4" ht="15">
+      <c r="A22" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:4" ht="16.5">
-      <c r="A5" s="21" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="14"/>
+    </row>
+    <row r="23" spans="1:4" ht="15">
+      <c r="A23" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24" spans="1:4" ht="15">
+      <c r="A24" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:4" ht="16.5">
-      <c r="A6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.5">
-      <c r="A7" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="1:4" ht="16.5">
-      <c r="A8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="19"/>
-    </row>
-    <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="1:4" ht="15">
+      <c r="A25" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="14"/>
+    </row>
+    <row r="26" spans="1:4" ht="15">
+      <c r="A26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="14"/>
+    </row>
+    <row r="28" spans="1:4" ht="15">
+      <c r="A28" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="14"/>
+    </row>
+    <row r="29" spans="1:4" ht="15">
+      <c r="A29" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" spans="1:4" ht="15">
+      <c r="A30" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="1:4" ht="15">
+      <c r="A31" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="15">
+      <c r="A32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="14"/>
+    </row>
+    <row r="33" spans="1:4" ht="15">
+      <c r="A33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" spans="1:4" ht="15">
+      <c r="A34" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" spans="1:4" ht="15">
+      <c r="A35" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="14"/>
+    </row>
+    <row r="36" spans="1:4" ht="15">
+      <c r="A36" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="B36" s="24"/>
+      <c r="C36" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="14"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
-      <c r="A10" s="23" t="s">
+    <row r="40" spans="1:4" ht="15.3">
+      <c r="A40" s="26"/>
+      <c r="B40" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="16.5">
-      <c r="A12" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="19"/>
-    </row>
-    <row r="13" spans="1:4" ht="16.5">
-      <c r="A13" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="25" t="s">
+      <c r="C40" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" spans="1:4" ht="16.5">
-      <c r="A14" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="19"/>
-    </row>
-    <row r="15" spans="1:4" ht="16.5">
-      <c r="A15" s="23" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="15.3">
+      <c r="A41" s="28"/>
+      <c r="B41" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="19"/>
-    </row>
-    <row r="16" spans="1:4" ht="16.5">
-      <c r="A16" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="19"/>
-    </row>
-    <row r="17" spans="1:4" ht="16.5">
-      <c r="A17" s="23" t="s">
+      <c r="C41" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.3">
+      <c r="A42" s="29"/>
+      <c r="B42" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="19"/>
-    </row>
-    <row r="18" spans="1:4" ht="16.5">
-      <c r="A18" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="19"/>
-    </row>
-    <row r="19" spans="1:4" ht="16.5">
-      <c r="A19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="19"/>
-    </row>
-    <row r="20" spans="1:4" ht="16.5">
-      <c r="A20" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="19"/>
-    </row>
-    <row r="21" spans="1:4" ht="16.5">
-      <c r="A21" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25" t="s">
+      <c r="C42" s="27" t="s">
         <v>59</v>
-      </c>
-      <c r="D21" s="19"/>
-    </row>
-    <row r="22" spans="1:4" ht="16.5">
-      <c r="A22" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="19"/>
-    </row>
-    <row r="23" spans="1:4" ht="16.5">
-      <c r="A23" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="19"/>
-    </row>
-    <row r="24" spans="1:4" ht="16.5">
-      <c r="A24" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="19"/>
-    </row>
-    <row r="25" spans="1:4" ht="16.5">
-      <c r="A25" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="19"/>
-    </row>
-    <row r="26" spans="1:4" ht="16.5">
-      <c r="A26" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="19"/>
-    </row>
-    <row r="27" spans="1:4" ht="16.5">
-      <c r="A27" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="19"/>
-    </row>
-    <row r="28" spans="1:4" ht="16.5">
-      <c r="A28" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="19"/>
-    </row>
-    <row r="29" spans="1:4" ht="16.5">
-      <c r="A29" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="19"/>
-    </row>
-    <row r="30" spans="1:4" ht="16.5">
-      <c r="A30" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="19"/>
-    </row>
-    <row r="31" spans="1:4" ht="16.5">
-      <c r="A31" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="19"/>
-    </row>
-    <row r="32" spans="1:4" ht="16.5">
-      <c r="A32" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="19"/>
-    </row>
-    <row r="33" spans="1:4" ht="16.5">
-      <c r="A33" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="19"/>
-    </row>
-    <row r="34" spans="1:4" ht="16.5">
-      <c r="A34" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="19"/>
-    </row>
-    <row r="35" spans="1:4" ht="16.5">
-      <c r="A35" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="19"/>
-    </row>
-    <row r="36" spans="1:4" ht="16.5">
-      <c r="A36" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="19"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="31"/>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="33"/>
-      <c r="B41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="34"/>
-      <c r="B42" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3601,7 +2873,7 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <conditionalFormatting sqref="C7">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>

--- a/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
+++ b/src/src/main/resources/template/APM_Asset_Dynamic_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\temp3\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD001E8-AD43-4AD5-9A11-BDAF96800553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1D28C-30A6-4284-A7DE-F660221C2031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset List" sheetId="2" r:id="rId1"/>
